--- a/governance_sheets/01_Role_Permission_Matrix.xlsx
+++ b/governance_sheets/01_Role_Permission_Matrix.xlsx
@@ -23,6 +23,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trainee" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IT Admin" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jr Engineer" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services Engineer" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3072,7 +3074,6 @@
           <t>pmc.measurement.create</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>Create measurement / RA bill</t>
@@ -3090,7 +3091,6 @@
           <t>pmc.measurement.add-items</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>Add measured quantities to RA bill</t>
@@ -3108,7 +3108,6 @@
           <t>finance.client-boq.edit-rate</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>Edit client BOQ rate</t>
@@ -3126,7 +3125,6 @@
           <t>finance.client-boq.edit-hsn</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>Edit client BOQ HSN</t>
@@ -3144,7 +3142,6 @@
           <t>onboarding.project-setup.edit-scope</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>Edit project setup scope</t>
@@ -3162,7 +3159,6 @@
           <t>workflow.submittal.review</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>Review submittal</t>
@@ -3180,7 +3176,6 @@
           <t>onboarding.boq.upload</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>Upload BOQ</t>
@@ -3198,7 +3193,6 @@
           <t>finance.payment.bulk-batch-export</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>Export ICICI bulk-payment batch</t>
@@ -5513,7 +5507,6 @@
           <t>pmc.measurement.create</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>Create measurement / RA bill</t>
@@ -5531,7 +5524,6 @@
           <t>pmc.measurement.add-items</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>Add measured quantities to RA bill</t>
@@ -5549,7 +5541,6 @@
           <t>finance.client-boq.edit-rate</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>Edit client BOQ rate</t>
@@ -5567,7 +5558,6 @@
           <t>finance.client-boq.edit-hsn</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>Edit client BOQ HSN</t>
@@ -5585,7 +5575,6 @@
           <t>onboarding.project-setup.edit-scope</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>Edit project setup scope</t>
@@ -5603,7 +5592,6 @@
           <t>workflow.submittal.review</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>Review submittal</t>
@@ -5621,7 +5609,6 @@
           <t>onboarding.boq.upload</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>Upload BOQ</t>
@@ -5639,7 +5626,6 @@
           <t>finance.payment.bulk-batch-export</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>Export ICICI bulk-payment batch</t>
@@ -7949,7 +7935,6 @@
           <t>pmc.measurement.create</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>Create measurement / RA bill</t>
@@ -7967,7 +7952,6 @@
           <t>pmc.measurement.add-items</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>Add measured quantities to RA bill</t>
@@ -7985,7 +7969,6 @@
           <t>finance.client-boq.edit-rate</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>Edit client BOQ rate</t>
@@ -8003,7 +7986,6 @@
           <t>finance.client-boq.edit-hsn</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>Edit client BOQ HSN</t>
@@ -8021,7 +8003,6 @@
           <t>onboarding.project-setup.edit-scope</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>Edit project setup scope</t>
@@ -8039,7 +8020,6 @@
           <t>workflow.submittal.review</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>Review submittal</t>
@@ -8057,7 +8037,6 @@
           <t>onboarding.boq.upload</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>Upload BOQ</t>
@@ -10389,7 +10368,6 @@
           <t>pmc.measurement.create</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>Create measurement / RA bill</t>
@@ -10407,7 +10385,6 @@
           <t>pmc.measurement.add-items</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>Add measured quantities to RA bill</t>
@@ -10425,7 +10402,6 @@
           <t>finance.client-boq.edit-rate</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>Edit client BOQ rate</t>
@@ -10443,7 +10419,6 @@
           <t>finance.client-boq.edit-hsn</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>Edit client BOQ HSN</t>
@@ -10461,7 +10436,6 @@
           <t>onboarding.project-setup.edit-scope</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>Edit project setup scope</t>
@@ -10479,7 +10453,6 @@
           <t>workflow.submittal.review</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>Review submittal</t>
@@ -10497,7 +10470,6 @@
           <t>onboarding.boq.upload</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>Upload BOQ</t>
@@ -10515,7 +10487,6 @@
           <t>finance.payment.bulk-batch-export</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>Export ICICI bulk-payment batch</t>
@@ -12820,7 +12791,6 @@
           <t>pmc.measurement.create</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>Create measurement / RA bill</t>
@@ -12838,7 +12808,6 @@
           <t>pmc.measurement.add-items</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>Add measured quantities to RA bill</t>
@@ -12856,7 +12825,6 @@
           <t>finance.client-boq.edit-rate</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>Edit client BOQ rate</t>
@@ -12874,7 +12842,6 @@
           <t>finance.client-boq.edit-hsn</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>Edit client BOQ HSN</t>
@@ -12892,7 +12859,6 @@
           <t>onboarding.project-setup.edit-scope</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>Edit project setup scope</t>
@@ -12910,7 +12876,6 @@
           <t>workflow.submittal.review</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>Review submittal</t>
@@ -12928,7 +12893,6 @@
           <t>onboarding.boq.upload</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>Upload BOQ</t>
@@ -12946,7 +12910,6 @@
           <t>finance.payment.bulk-batch-export</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>Export ICICI bulk-payment batch</t>
@@ -15246,7 +15209,6 @@
           <t>pmc.measurement.create</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>Create measurement / RA bill</t>
@@ -15264,7 +15226,6 @@
           <t>pmc.measurement.add-items</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>Add measured quantities to RA bill</t>
@@ -15282,7 +15243,6 @@
           <t>finance.client-boq.edit-rate</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>Edit client BOQ rate</t>
@@ -15300,7 +15260,6 @@
           <t>finance.client-boq.edit-hsn</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>Edit client BOQ HSN</t>
@@ -15318,7 +15277,6 @@
           <t>onboarding.project-setup.edit-scope</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>Edit project setup scope</t>
@@ -15336,7 +15294,6 @@
           <t>workflow.submittal.review</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>Review submittal</t>
@@ -15354,7 +15311,6 @@
           <t>onboarding.boq.upload</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>Upload BOQ</t>
@@ -17676,7 +17632,6 @@
           <t>pmc.measurement.create</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>Create measurement / RA bill</t>
@@ -17694,7 +17649,6 @@
           <t>pmc.measurement.add-items</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>Add measured quantities to RA bill</t>
@@ -17712,7 +17666,6 @@
           <t>finance.client-boq.edit-rate</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>Edit client BOQ rate</t>
@@ -17730,7 +17683,6 @@
           <t>finance.client-boq.edit-hsn</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>Edit client BOQ HSN</t>
@@ -17748,7 +17700,6 @@
           <t>onboarding.project-setup.edit-scope</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>Edit project setup scope</t>
@@ -17766,7 +17717,6 @@
           <t>workflow.submittal.review</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>Review submittal</t>
@@ -17784,7 +17734,6 @@
           <t>onboarding.boq.upload</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>Upload BOQ</t>
@@ -17802,7 +17751,4862 @@
           <t>finance.payment.bulk-batch-export</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Export ICICI bulk-payment batch</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A118:D118"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A107:D107"/>
+    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="A111:D111"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="003DAA6E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D140"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>nu PMC — Jr Engineer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>What this role can do. W=Write R=Read A=Approve —=No access</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Action / Responsibility</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Access</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="26" t="n"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>View petty cash</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr"/>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>Create petty cash entry</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr"/>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Replenish petty cash</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>View direct payments</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Record direct payment</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>View client receipts</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Record client receipt</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>View advance recovery</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr"/>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Record advance recovery</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>View payment requests</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Raise payment request</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>Raise urgent payment</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>PMC approve payment request</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>Principal approve payment request</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Clear vendor (finance)</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>Validate vendor PAN</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr"/>
+    </row>
+    <row r="22" ht="14" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="n"/>
+      <c r="C22" s="25" t="n"/>
+      <c r="D22" s="26" t="n"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>View drawings</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Upload drawing</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr"/>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>Approve / reject drawing (L2)</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>View drawing register</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr"/>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>Upload to drawing register</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr"/>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>View submittals</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr"/>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>Create submittal</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr"/>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>Review submittal</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr"/>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>Answer drawing RFI</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr"/>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>View form templates</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>Create form template</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr"/>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>Approve form template</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr"/>
+    </row>
+    <row r="35" ht="14" customHeight="1">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="n"/>
+      <c r="C35" s="25" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>View measurements</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="inlineStr"/>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>Create measurement</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr"/>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>Add measurement items</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="inlineStr"/>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>Stream sign-off measurement</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="inlineStr"/>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>Record client acceptance</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="inlineStr"/>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>View claims</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="inlineStr"/>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>Raise claim</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr"/>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>Add claim items</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D43" s="22" t="inlineStr"/>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>PMC sign-off claim</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="inlineStr"/>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>Stream sign-off claim</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="inlineStr"/>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>Approve claim (final)</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr"/>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>Record invoice number on claim</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D47" s="22" t="inlineStr"/>
+    </row>
+    <row r="48" ht="14" customHeight="1">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B48" s="25" t="n"/>
+      <c r="C48" s="25" t="n"/>
+      <c r="D48" s="26" t="n"/>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>View schedule</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D49" s="22" t="inlineStr"/>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>Update task progress</t>
+        </is>
+      </c>
+      <c r="C50" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr"/>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>View GRNs</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D51" s="22" t="inlineStr"/>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>Create GRN</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="inlineStr"/>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>Approve GRN</t>
+        </is>
+      </c>
+      <c r="C53" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D53" s="22" t="inlineStr"/>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B54" s="16" t="inlineStr">
+        <is>
+          <t>Flag GRN non-conformance</t>
+        </is>
+      </c>
+      <c r="C54" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D54" s="18" t="inlineStr"/>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="inlineStr">
+        <is>
+          <t>View snags</t>
+        </is>
+      </c>
+      <c r="C55" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D55" s="22" t="inlineStr"/>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B56" s="16" t="inlineStr">
+        <is>
+          <t>Raise snag</t>
+        </is>
+      </c>
+      <c r="C56" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D56" s="18" t="inlineStr"/>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B57" s="20" t="inlineStr">
+        <is>
+          <t>Mark snag rectified</t>
+        </is>
+      </c>
+      <c r="C57" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D57" s="22" t="inlineStr"/>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>Close snag (verify)</t>
+        </is>
+      </c>
+      <c r="C58" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D58" s="18" t="inlineStr"/>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B59" s="20" t="inlineStr">
+        <is>
+          <t>View photos</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D59" s="22" t="inlineStr"/>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B60" s="16" t="inlineStr">
+        <is>
+          <t>Upload site photo</t>
+        </is>
+      </c>
+      <c r="C60" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D60" s="18" t="inlineStr"/>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B61" s="20" t="inlineStr">
+        <is>
+          <t>Upload project document</t>
+        </is>
+      </c>
+      <c r="C61" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D61" s="22" t="inlineStr"/>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B62" s="16" t="inlineStr">
+        <is>
+          <t>View issues</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D62" s="18" t="inlineStr"/>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B63" s="20" t="inlineStr">
+        <is>
+          <t>Raise issue</t>
+        </is>
+      </c>
+      <c r="C63" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D63" s="22" t="inlineStr"/>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>Close issue</t>
+        </is>
+      </c>
+      <c r="C64" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D64" s="18" t="inlineStr"/>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B65" s="20" t="inlineStr">
+        <is>
+          <t>Raise drawing RFI</t>
+        </is>
+      </c>
+      <c r="C65" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D65" s="22" t="inlineStr"/>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B66" s="16" t="inlineStr">
+        <is>
+          <t>View meetings / MOMs</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D66" s="18" t="inlineStr"/>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B67" s="20" t="inlineStr">
+        <is>
+          <t>Create meeting / MOM (draft)</t>
+        </is>
+      </c>
+      <c r="C67" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D67" s="22" t="inlineStr"/>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B68" s="16" t="inlineStr">
+        <is>
+          <t>Log site visit</t>
+        </is>
+      </c>
+      <c r="C68" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="inlineStr"/>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B69" s="20" t="inlineStr">
+        <is>
+          <t>Add observation to meeting</t>
+        </is>
+      </c>
+      <c r="C69" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D69" s="22" t="inlineStr"/>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B70" s="16" t="inlineStr">
+        <is>
+          <t>Upload file to meeting</t>
+        </is>
+      </c>
+      <c r="C70" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="18" t="inlineStr"/>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B71" s="20" t="inlineStr">
+        <is>
+          <t>Acknowledge own meeting action item</t>
+        </is>
+      </c>
+      <c r="C71" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D71" s="22" t="inlineStr"/>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>Complete own meeting action item</t>
+        </is>
+      </c>
+      <c r="C72" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D72" s="18" t="inlineStr"/>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B73" s="20" t="inlineStr">
+        <is>
+          <t>Log client communication</t>
+        </is>
+      </c>
+      <c r="C73" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D73" s="22" t="inlineStr"/>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>Submit form (fill and send)</t>
+        </is>
+      </c>
+      <c r="C74" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D74" s="18" t="inlineStr"/>
+    </row>
+    <row r="75" ht="14" customHeight="1">
+      <c r="A75" s="14" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B75" s="25" t="n"/>
+      <c r="C75" s="25" t="n"/>
+      <c r="D75" s="26" t="n"/>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="15" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B76" s="16" t="inlineStr">
+        <is>
+          <t>View change notices</t>
+        </is>
+      </c>
+      <c r="C76" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D76" s="18" t="inlineStr"/>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="19" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B77" s="20" t="inlineStr">
+        <is>
+          <t>Raise change notice</t>
+        </is>
+      </c>
+      <c r="C77" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D77" s="22" t="inlineStr"/>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="15" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B78" s="16" t="inlineStr">
+        <is>
+          <t>Sign change notice</t>
+        </is>
+      </c>
+      <c r="C78" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="18" t="inlineStr"/>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="19" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B79" s="20" t="inlineStr">
+        <is>
+          <t>Approve change notice</t>
+        </is>
+      </c>
+      <c r="C79" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="22" t="inlineStr"/>
+    </row>
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="15" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B80" s="16" t="inlineStr">
+        <is>
+          <t>View weekly reports</t>
+        </is>
+      </c>
+      <c r="C80" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D80" s="18" t="inlineStr"/>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="19" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B81" s="20" t="inlineStr">
+        <is>
+          <t>Edit PMC section</t>
+        </is>
+      </c>
+      <c r="C81" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="22" t="inlineStr"/>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="15" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B82" s="16" t="inlineStr">
+        <is>
+          <t>Edit design section</t>
+        </is>
+      </c>
+      <c r="C82" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="18" t="inlineStr"/>
+    </row>
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="19" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B83" s="20" t="inlineStr">
+        <is>
+          <t>Edit services section</t>
+        </is>
+      </c>
+      <c r="C83" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D83" s="22" t="inlineStr"/>
+    </row>
+    <row r="84" ht="16" customHeight="1">
+      <c r="A84" s="15" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B84" s="16" t="inlineStr">
+        <is>
+          <t>Sign weekly report section</t>
+        </is>
+      </c>
+      <c r="C84" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D84" s="18" t="inlineStr"/>
+    </row>
+    <row r="85" ht="16" customHeight="1">
+      <c r="A85" s="19" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B85" s="20" t="inlineStr">
+        <is>
+          <t>Mark weekly report sent to client</t>
+        </is>
+      </c>
+      <c r="C85" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D85" s="22" t="inlineStr"/>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="15" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B86" s="16" t="inlineStr">
+        <is>
+          <t>Acknowledge AI anomaly flag</t>
+        </is>
+      </c>
+      <c r="C86" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D86" s="18" t="inlineStr"/>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="19" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B87" s="20" t="inlineStr">
+        <is>
+          <t>Reset another user's password</t>
+        </is>
+      </c>
+      <c r="C87" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D87" s="22" t="inlineStr"/>
+    </row>
+    <row r="88" ht="14" customHeight="1">
+      <c r="A88" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B88" s="25" t="n"/>
+      <c r="C88" s="25" t="n"/>
+      <c r="D88" s="26" t="n"/>
+    </row>
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B89" s="20" t="inlineStr">
+        <is>
+          <t>Initiate new user</t>
+        </is>
+      </c>
+      <c r="C89" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D89" s="22" t="inlineStr"/>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B90" s="16" t="inlineStr">
+        <is>
+          <t>Approve new user</t>
+        </is>
+      </c>
+      <c r="C90" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D90" s="18" t="inlineStr"/>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B91" s="20" t="inlineStr">
+        <is>
+          <t>View vendor master</t>
+        </is>
+      </c>
+      <c r="C91" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D91" s="22" t="inlineStr"/>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B92" s="16" t="inlineStr">
+        <is>
+          <t>Create vendor master entry</t>
+        </is>
+      </c>
+      <c r="C92" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D92" s="18" t="inlineStr"/>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B93" s="20" t="inlineStr">
+        <is>
+          <t>Edit nav / role tabs</t>
+        </is>
+      </c>
+      <c r="C93" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D93" s="22" t="inlineStr"/>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B94" s="16" t="inlineStr">
+        <is>
+          <t>Manage delegations</t>
+        </is>
+      </c>
+      <c r="C94" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D94" s="18" t="inlineStr"/>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B95" s="20" t="inlineStr">
+        <is>
+          <t>Project setup</t>
+        </is>
+      </c>
+      <c r="C95" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D95" s="22" t="inlineStr"/>
+    </row>
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B96" s="16" t="inlineStr">
+        <is>
+          <t>Trigger AI photo tag</t>
+        </is>
+      </c>
+      <c r="C96" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D96" s="18" t="inlineStr"/>
+    </row>
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B97" s="20" t="inlineStr">
+        <is>
+          <t>vendors.create</t>
+        </is>
+      </c>
+      <c r="C97" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D97" s="22" t="inlineStr"/>
+    </row>
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B98" s="16" t="inlineStr">
+        <is>
+          <t>users.bulk_upload</t>
+        </is>
+      </c>
+      <c r="C98" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D98" s="18" t="inlineStr"/>
+    </row>
+    <row r="99" ht="16" customHeight="1">
+      <c r="A99" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B99" s="20" t="inlineStr">
+        <is>
+          <t>users.deactivate</t>
+        </is>
+      </c>
+      <c r="C99" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D99" s="22" t="inlineStr"/>
+    </row>
+    <row r="100" ht="16" customHeight="1">
+      <c r="A100" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B100" s="16" t="inlineStr">
+        <is>
+          <t>clients.create</t>
+        </is>
+      </c>
+      <c r="C100" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D100" s="18" t="inlineStr"/>
+    </row>
+    <row r="101" ht="16" customHeight="1">
+      <c r="A101" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B101" s="20" t="inlineStr">
+        <is>
+          <t>clients.edit</t>
+        </is>
+      </c>
+      <c r="C101" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D101" s="22" t="inlineStr"/>
+    </row>
+    <row r="102" ht="16" customHeight="1">
+      <c r="A102" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B102" s="16" t="inlineStr">
+        <is>
+          <t>clients.bulk_upload</t>
+        </is>
+      </c>
+      <c r="C102" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D102" s="18" t="inlineStr"/>
+    </row>
+    <row r="103" ht="16" customHeight="1">
+      <c r="A103" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B103" s="20" t="inlineStr">
+        <is>
+          <t>vendors.bulk_upload</t>
+        </is>
+      </c>
+      <c r="C103" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D103" s="22" t="inlineStr"/>
+    </row>
+    <row r="104" ht="16" customHeight="1">
+      <c r="A104" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B104" s="16" t="inlineStr">
+        <is>
+          <t>vendors.engage</t>
+        </is>
+      </c>
+      <c r="C104" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D104" s="18" t="inlineStr"/>
+    </row>
+    <row r="105" ht="16" customHeight="1">
+      <c r="A105" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B105" s="20" t="inlineStr">
+        <is>
+          <t>projects.create</t>
+        </is>
+      </c>
+      <c r="C105" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D105" s="22" t="inlineStr"/>
+    </row>
+    <row r="106" ht="16" customHeight="1">
+      <c r="A106" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B106" s="16" t="inlineStr">
+        <is>
+          <t>projects.edit</t>
+        </is>
+      </c>
+      <c r="C106" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D106" s="18" t="inlineStr"/>
+    </row>
+    <row r="107" ht="14" customHeight="1">
+      <c r="A107" s="14" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B107" s="25" t="n"/>
+      <c r="C107" s="25" t="n"/>
+      <c r="D107" s="26" t="n"/>
+    </row>
+    <row r="108" ht="16" customHeight="1">
+      <c r="A108" s="15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B108" s="16" t="inlineStr">
+        <is>
+          <t>invoices.raise</t>
+        </is>
+      </c>
+      <c r="C108" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D108" s="18" t="inlineStr"/>
+    </row>
+    <row r="109" ht="16" customHeight="1">
+      <c r="A109" s="19" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B109" s="20" t="inlineStr">
+        <is>
+          <t>payments.execute</t>
+        </is>
+      </c>
+      <c r="C109" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D109" s="22" t="inlineStr"/>
+    </row>
+    <row r="110" ht="16" customHeight="1">
+      <c r="A110" s="15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B110" s="16" t="inlineStr">
+        <is>
+          <t>gst.view</t>
+        </is>
+      </c>
+      <c r="C110" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D110" s="18" t="inlineStr"/>
+    </row>
+    <row r="111" ht="14" customHeight="1">
+      <c r="A111" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B111" s="25" t="n"/>
+      <c r="C111" s="25" t="n"/>
+      <c r="D111" s="26" t="n"/>
+    </row>
+    <row r="112" ht="16" customHeight="1">
+      <c r="A112" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B112" s="16" t="inlineStr">
+        <is>
+          <t>boq.upload</t>
+        </is>
+      </c>
+      <c r="C112" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D112" s="18" t="inlineStr"/>
+    </row>
+    <row r="113" ht="16" customHeight="1">
+      <c r="A113" s="19" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B113" s="20" t="inlineStr">
+        <is>
+          <t>boq.map</t>
+        </is>
+      </c>
+      <c r="C113" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D113" s="22" t="inlineStr"/>
+    </row>
+    <row r="114" ht="16" customHeight="1">
+      <c r="A114" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B114" s="16" t="inlineStr">
+        <is>
+          <t>budget.approve</t>
+        </is>
+      </c>
+      <c r="C114" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D114" s="18" t="inlineStr"/>
+    </row>
+    <row r="115" ht="14" customHeight="1">
+      <c r="A115" s="14" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B115" s="25" t="n"/>
+      <c r="C115" s="25" t="n"/>
+      <c r="D115" s="26" t="n"/>
+    </row>
+    <row r="116" ht="16" customHeight="1">
+      <c r="A116" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B116" s="16" t="inlineStr">
+        <is>
+          <t>mom.issue</t>
+        </is>
+      </c>
+      <c r="C116" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D116" s="18" t="inlineStr"/>
+    </row>
+    <row r="117" ht="16" customHeight="1">
+      <c r="A117" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B117" s="20" t="inlineStr">
+        <is>
+          <t>mom.sign</t>
+        </is>
+      </c>
+      <c r="C117" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D117" s="22" t="inlineStr"/>
+    </row>
+    <row r="118" ht="14" customHeight="1">
+      <c r="A118" s="14" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B118" s="25" t="n"/>
+      <c r="C118" s="25" t="n"/>
+      <c r="D118" s="26" t="n"/>
+    </row>
+    <row r="119" ht="16" customHeight="1">
+      <c r="A119" s="19" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B119" s="20" t="inlineStr">
+        <is>
+          <t>reports.approve</t>
+        </is>
+      </c>
+      <c r="C119" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D119" s="22" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>finance.payment-request.mark-paid</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Mark payment request as paid</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>finance.payment.pre-upload-check</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Pre-upload payment validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>pmc.issue.close-resolved</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Close resolved issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>pmc.issue.reactivate</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Reopen closed issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>pmc.issue.snag-raise</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Raise DLP defect</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>pmc.issue.snag-resolve</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Mark defect as fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>pmc.issue.snag-signoff</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Sign off resolved snag</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>pmc.handover.checklist-init</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Initialise handover checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>pmc.handover.checklist-upload</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Upload handover document</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>pmc.handover.closure-signoff</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Sign off project closure</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>pmc.lessons.input-write</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Write lessons-learned input</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>pmc.lessons.report-view</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>View consolidated lessons report</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>pmc.lessons.publish</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Publish lessons to firm Knowledge Library</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>pmc.measurement.create</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Create measurement / RA bill</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>pmc.measurement.add-items</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Add measured quantities to RA bill</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>finance.client-boq.edit-rate</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Edit client BOQ rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>finance.client-boq.edit-hsn</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Edit client BOQ HSN</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>onboarding.project-setup.edit-scope</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Edit project setup scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Workflow</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>workflow.submittal.review</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Review submittal</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>onboarding.boq.upload</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Upload BOQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>finance.payment.bulk-batch-export</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Export ICICI bulk-payment batch</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A118:D118"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A107:D107"/>
+    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="A111:D111"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="003DAA6E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D140"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>nu PMC — Services Engineer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>What this role can do. W=Write R=Read A=Approve —=No access</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Action / Responsibility</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Access</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="26" t="n"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>View petty cash</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr"/>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>Create petty cash entry</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr"/>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Replenish petty cash</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>View direct payments</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Record direct payment</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>View client receipts</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Record client receipt</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>View advance recovery</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr"/>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Record advance recovery</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>View payment requests</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Raise payment request</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>Raise urgent payment</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>PMC approve payment request</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>Principal approve payment request</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Clear vendor (finance)</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>Validate vendor PAN</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr"/>
+    </row>
+    <row r="22" ht="14" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="n"/>
+      <c r="C22" s="25" t="n"/>
+      <c r="D22" s="26" t="n"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>View drawings</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Upload drawing</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr"/>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>Approve / reject drawing (L2)</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>View drawing register</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr"/>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>Upload to drawing register</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr"/>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>View submittals</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr"/>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>Create submittal</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr"/>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>Review submittal</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr"/>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>Answer drawing RFI</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr"/>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>View form templates</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>Create form template</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr"/>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>Approve form template</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr"/>
+    </row>
+    <row r="35" ht="14" customHeight="1">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="n"/>
+      <c r="C35" s="25" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>View measurements</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="inlineStr"/>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>Create measurement</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr"/>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>Add measurement items</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="inlineStr"/>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>Stream sign-off measurement</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="inlineStr"/>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>Record client acceptance</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="inlineStr"/>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>View claims</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="inlineStr"/>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>Raise claim</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr"/>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>Add claim items</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D43" s="22" t="inlineStr"/>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>PMC sign-off claim</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="inlineStr"/>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>Stream sign-off claim</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="inlineStr"/>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>Approve claim (final)</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr"/>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>Record invoice number on claim</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D47" s="22" t="inlineStr"/>
+    </row>
+    <row r="48" ht="14" customHeight="1">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B48" s="25" t="n"/>
+      <c r="C48" s="25" t="n"/>
+      <c r="D48" s="26" t="n"/>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>View schedule</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D49" s="22" t="inlineStr"/>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>Update task progress</t>
+        </is>
+      </c>
+      <c r="C50" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr"/>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>View GRNs</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D51" s="22" t="inlineStr"/>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>Create GRN</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="inlineStr"/>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>Approve GRN</t>
+        </is>
+      </c>
+      <c r="C53" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D53" s="22" t="inlineStr"/>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B54" s="16" t="inlineStr">
+        <is>
+          <t>Flag GRN non-conformance</t>
+        </is>
+      </c>
+      <c r="C54" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D54" s="18" t="inlineStr"/>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="inlineStr">
+        <is>
+          <t>View snags</t>
+        </is>
+      </c>
+      <c r="C55" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D55" s="22" t="inlineStr"/>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B56" s="16" t="inlineStr">
+        <is>
+          <t>Raise snag</t>
+        </is>
+      </c>
+      <c r="C56" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D56" s="18" t="inlineStr"/>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B57" s="20" t="inlineStr">
+        <is>
+          <t>Mark snag rectified</t>
+        </is>
+      </c>
+      <c r="C57" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D57" s="22" t="inlineStr"/>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>Close snag (verify)</t>
+        </is>
+      </c>
+      <c r="C58" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D58" s="18" t="inlineStr"/>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B59" s="20" t="inlineStr">
+        <is>
+          <t>View photos</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D59" s="22" t="inlineStr"/>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B60" s="16" t="inlineStr">
+        <is>
+          <t>Upload site photo</t>
+        </is>
+      </c>
+      <c r="C60" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D60" s="18" t="inlineStr"/>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B61" s="20" t="inlineStr">
+        <is>
+          <t>Upload project document</t>
+        </is>
+      </c>
+      <c r="C61" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D61" s="22" t="inlineStr"/>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B62" s="16" t="inlineStr">
+        <is>
+          <t>View issues</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D62" s="18" t="inlineStr"/>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B63" s="20" t="inlineStr">
+        <is>
+          <t>Raise issue</t>
+        </is>
+      </c>
+      <c r="C63" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D63" s="22" t="inlineStr"/>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>Close issue</t>
+        </is>
+      </c>
+      <c r="C64" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D64" s="18" t="inlineStr"/>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B65" s="20" t="inlineStr">
+        <is>
+          <t>Raise drawing RFI</t>
+        </is>
+      </c>
+      <c r="C65" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D65" s="22" t="inlineStr"/>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B66" s="16" t="inlineStr">
+        <is>
+          <t>View meetings / MOMs</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D66" s="18" t="inlineStr"/>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B67" s="20" t="inlineStr">
+        <is>
+          <t>Create meeting / MOM (draft)</t>
+        </is>
+      </c>
+      <c r="C67" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D67" s="22" t="inlineStr"/>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B68" s="16" t="inlineStr">
+        <is>
+          <t>Log site visit</t>
+        </is>
+      </c>
+      <c r="C68" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="inlineStr"/>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B69" s="20" t="inlineStr">
+        <is>
+          <t>Add observation to meeting</t>
+        </is>
+      </c>
+      <c r="C69" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D69" s="22" t="inlineStr"/>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B70" s="16" t="inlineStr">
+        <is>
+          <t>Upload file to meeting</t>
+        </is>
+      </c>
+      <c r="C70" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="18" t="inlineStr"/>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B71" s="20" t="inlineStr">
+        <is>
+          <t>Acknowledge own meeting action item</t>
+        </is>
+      </c>
+      <c r="C71" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D71" s="22" t="inlineStr"/>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>Complete own meeting action item</t>
+        </is>
+      </c>
+      <c r="C72" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D72" s="18" t="inlineStr"/>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B73" s="20" t="inlineStr">
+        <is>
+          <t>Log client communication</t>
+        </is>
+      </c>
+      <c r="C73" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D73" s="22" t="inlineStr"/>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>Submit form (fill and send)</t>
+        </is>
+      </c>
+      <c r="C74" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D74" s="18" t="inlineStr"/>
+    </row>
+    <row r="75" ht="14" customHeight="1">
+      <c r="A75" s="14" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B75" s="25" t="n"/>
+      <c r="C75" s="25" t="n"/>
+      <c r="D75" s="26" t="n"/>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="15" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B76" s="16" t="inlineStr">
+        <is>
+          <t>View change notices</t>
+        </is>
+      </c>
+      <c r="C76" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D76" s="18" t="inlineStr"/>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="19" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B77" s="20" t="inlineStr">
+        <is>
+          <t>Raise change notice</t>
+        </is>
+      </c>
+      <c r="C77" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D77" s="22" t="inlineStr"/>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="15" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B78" s="16" t="inlineStr">
+        <is>
+          <t>Sign change notice</t>
+        </is>
+      </c>
+      <c r="C78" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="18" t="inlineStr"/>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="19" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B79" s="20" t="inlineStr">
+        <is>
+          <t>Approve change notice</t>
+        </is>
+      </c>
+      <c r="C79" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="22" t="inlineStr"/>
+    </row>
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="15" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B80" s="16" t="inlineStr">
+        <is>
+          <t>View weekly reports</t>
+        </is>
+      </c>
+      <c r="C80" s="17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D80" s="18" t="inlineStr"/>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="19" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B81" s="20" t="inlineStr">
+        <is>
+          <t>Edit PMC section</t>
+        </is>
+      </c>
+      <c r="C81" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="22" t="inlineStr"/>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="15" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B82" s="16" t="inlineStr">
+        <is>
+          <t>Edit design section</t>
+        </is>
+      </c>
+      <c r="C82" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="18" t="inlineStr"/>
+    </row>
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="19" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B83" s="20" t="inlineStr">
+        <is>
+          <t>Edit services section</t>
+        </is>
+      </c>
+      <c r="C83" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D83" s="22" t="inlineStr"/>
+    </row>
+    <row r="84" ht="16" customHeight="1">
+      <c r="A84" s="15" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B84" s="16" t="inlineStr">
+        <is>
+          <t>Sign weekly report section</t>
+        </is>
+      </c>
+      <c r="C84" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D84" s="18" t="inlineStr"/>
+    </row>
+    <row r="85" ht="16" customHeight="1">
+      <c r="A85" s="19" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B85" s="20" t="inlineStr">
+        <is>
+          <t>Mark weekly report sent to client</t>
+        </is>
+      </c>
+      <c r="C85" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D85" s="22" t="inlineStr"/>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="15" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B86" s="16" t="inlineStr">
+        <is>
+          <t>Acknowledge AI anomaly flag</t>
+        </is>
+      </c>
+      <c r="C86" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D86" s="18" t="inlineStr"/>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="19" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B87" s="20" t="inlineStr">
+        <is>
+          <t>Reset another user's password</t>
+        </is>
+      </c>
+      <c r="C87" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D87" s="22" t="inlineStr"/>
+    </row>
+    <row r="88" ht="14" customHeight="1">
+      <c r="A88" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B88" s="25" t="n"/>
+      <c r="C88" s="25" t="n"/>
+      <c r="D88" s="26" t="n"/>
+    </row>
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B89" s="20" t="inlineStr">
+        <is>
+          <t>Initiate new user</t>
+        </is>
+      </c>
+      <c r="C89" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D89" s="22" t="inlineStr"/>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B90" s="16" t="inlineStr">
+        <is>
+          <t>Approve new user</t>
+        </is>
+      </c>
+      <c r="C90" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D90" s="18" t="inlineStr"/>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B91" s="20" t="inlineStr">
+        <is>
+          <t>View vendor master</t>
+        </is>
+      </c>
+      <c r="C91" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D91" s="22" t="inlineStr"/>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B92" s="16" t="inlineStr">
+        <is>
+          <t>Create vendor master entry</t>
+        </is>
+      </c>
+      <c r="C92" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D92" s="18" t="inlineStr"/>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B93" s="20" t="inlineStr">
+        <is>
+          <t>Edit nav / role tabs</t>
+        </is>
+      </c>
+      <c r="C93" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D93" s="22" t="inlineStr"/>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B94" s="16" t="inlineStr">
+        <is>
+          <t>Manage delegations</t>
+        </is>
+      </c>
+      <c r="C94" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D94" s="18" t="inlineStr"/>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B95" s="20" t="inlineStr">
+        <is>
+          <t>Project setup</t>
+        </is>
+      </c>
+      <c r="C95" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D95" s="22" t="inlineStr"/>
+    </row>
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B96" s="16" t="inlineStr">
+        <is>
+          <t>Trigger AI photo tag</t>
+        </is>
+      </c>
+      <c r="C96" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D96" s="18" t="inlineStr"/>
+    </row>
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B97" s="20" t="inlineStr">
+        <is>
+          <t>vendors.create</t>
+        </is>
+      </c>
+      <c r="C97" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D97" s="22" t="inlineStr"/>
+    </row>
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B98" s="16" t="inlineStr">
+        <is>
+          <t>users.bulk_upload</t>
+        </is>
+      </c>
+      <c r="C98" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D98" s="18" t="inlineStr"/>
+    </row>
+    <row r="99" ht="16" customHeight="1">
+      <c r="A99" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B99" s="20" t="inlineStr">
+        <is>
+          <t>users.deactivate</t>
+        </is>
+      </c>
+      <c r="C99" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D99" s="22" t="inlineStr"/>
+    </row>
+    <row r="100" ht="16" customHeight="1">
+      <c r="A100" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B100" s="16" t="inlineStr">
+        <is>
+          <t>clients.create</t>
+        </is>
+      </c>
+      <c r="C100" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D100" s="18" t="inlineStr"/>
+    </row>
+    <row r="101" ht="16" customHeight="1">
+      <c r="A101" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B101" s="20" t="inlineStr">
+        <is>
+          <t>clients.edit</t>
+        </is>
+      </c>
+      <c r="C101" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D101" s="22" t="inlineStr"/>
+    </row>
+    <row r="102" ht="16" customHeight="1">
+      <c r="A102" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B102" s="16" t="inlineStr">
+        <is>
+          <t>clients.bulk_upload</t>
+        </is>
+      </c>
+      <c r="C102" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D102" s="18" t="inlineStr"/>
+    </row>
+    <row r="103" ht="16" customHeight="1">
+      <c r="A103" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B103" s="20" t="inlineStr">
+        <is>
+          <t>vendors.bulk_upload</t>
+        </is>
+      </c>
+      <c r="C103" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D103" s="22" t="inlineStr"/>
+    </row>
+    <row r="104" ht="16" customHeight="1">
+      <c r="A104" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B104" s="16" t="inlineStr">
+        <is>
+          <t>vendors.engage</t>
+        </is>
+      </c>
+      <c r="C104" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D104" s="18" t="inlineStr"/>
+    </row>
+    <row r="105" ht="16" customHeight="1">
+      <c r="A105" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B105" s="20" t="inlineStr">
+        <is>
+          <t>projects.create</t>
+        </is>
+      </c>
+      <c r="C105" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D105" s="22" t="inlineStr"/>
+    </row>
+    <row r="106" ht="16" customHeight="1">
+      <c r="A106" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="B106" s="16" t="inlineStr">
+        <is>
+          <t>projects.edit</t>
+        </is>
+      </c>
+      <c r="C106" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D106" s="18" t="inlineStr"/>
+    </row>
+    <row r="107" ht="14" customHeight="1">
+      <c r="A107" s="14" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B107" s="25" t="n"/>
+      <c r="C107" s="25" t="n"/>
+      <c r="D107" s="26" t="n"/>
+    </row>
+    <row r="108" ht="16" customHeight="1">
+      <c r="A108" s="15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B108" s="16" t="inlineStr">
+        <is>
+          <t>invoices.raise</t>
+        </is>
+      </c>
+      <c r="C108" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D108" s="18" t="inlineStr"/>
+    </row>
+    <row r="109" ht="16" customHeight="1">
+      <c r="A109" s="19" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B109" s="20" t="inlineStr">
+        <is>
+          <t>payments.execute</t>
+        </is>
+      </c>
+      <c r="C109" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D109" s="22" t="inlineStr"/>
+    </row>
+    <row r="110" ht="16" customHeight="1">
+      <c r="A110" s="15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B110" s="16" t="inlineStr">
+        <is>
+          <t>gst.view</t>
+        </is>
+      </c>
+      <c r="C110" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D110" s="18" t="inlineStr"/>
+    </row>
+    <row r="111" ht="14" customHeight="1">
+      <c r="A111" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B111" s="25" t="n"/>
+      <c r="C111" s="25" t="n"/>
+      <c r="D111" s="26" t="n"/>
+    </row>
+    <row r="112" ht="16" customHeight="1">
+      <c r="A112" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B112" s="16" t="inlineStr">
+        <is>
+          <t>boq.upload</t>
+        </is>
+      </c>
+      <c r="C112" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D112" s="18" t="inlineStr"/>
+    </row>
+    <row r="113" ht="16" customHeight="1">
+      <c r="A113" s="19" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B113" s="20" t="inlineStr">
+        <is>
+          <t>boq.map</t>
+        </is>
+      </c>
+      <c r="C113" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D113" s="22" t="inlineStr"/>
+    </row>
+    <row r="114" ht="16" customHeight="1">
+      <c r="A114" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B114" s="16" t="inlineStr">
+        <is>
+          <t>budget.approve</t>
+        </is>
+      </c>
+      <c r="C114" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D114" s="18" t="inlineStr"/>
+    </row>
+    <row r="115" ht="14" customHeight="1">
+      <c r="A115" s="14" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B115" s="25" t="n"/>
+      <c r="C115" s="25" t="n"/>
+      <c r="D115" s="26" t="n"/>
+    </row>
+    <row r="116" ht="16" customHeight="1">
+      <c r="A116" s="15" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B116" s="16" t="inlineStr">
+        <is>
+          <t>mom.issue</t>
+        </is>
+      </c>
+      <c r="C116" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D116" s="18" t="inlineStr"/>
+    </row>
+    <row r="117" ht="16" customHeight="1">
+      <c r="A117" s="19" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B117" s="20" t="inlineStr">
+        <is>
+          <t>mom.sign</t>
+        </is>
+      </c>
+      <c r="C117" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D117" s="22" t="inlineStr"/>
+    </row>
+    <row r="118" ht="14" customHeight="1">
+      <c r="A118" s="14" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B118" s="25" t="n"/>
+      <c r="C118" s="25" t="n"/>
+      <c r="D118" s="26" t="n"/>
+    </row>
+    <row r="119" ht="16" customHeight="1">
+      <c r="A119" s="19" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B119" s="20" t="inlineStr">
+        <is>
+          <t>reports.approve</t>
+        </is>
+      </c>
+      <c r="C119" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D119" s="22" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>finance.payment-request.mark-paid</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Mark payment request as paid</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>finance.payment.pre-upload-check</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Pre-upload payment validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>pmc.issue.close-resolved</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Close resolved issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>pmc.issue.reactivate</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Reopen closed issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>pmc.issue.snag-raise</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Raise DLP defect</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>pmc.issue.snag-resolve</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Mark defect as fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>pmc.issue.snag-signoff</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Sign off resolved snag</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>pmc.handover.checklist-init</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Initialise handover checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>pmc.handover.checklist-upload</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Upload handover document</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>pmc.handover.closure-signoff</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Sign off project closure</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>pmc.lessons.input-write</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Write lessons-learned input</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>pmc.lessons.report-view</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>View consolidated lessons report</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>pmc.lessons.publish</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Publish lessons to firm Knowledge Library</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>pmc.measurement.create</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Create measurement / RA bill</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>PMC / Site</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>pmc.measurement.add-items</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Add measured quantities to RA bill</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>finance.client-boq.edit-rate</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Edit client BOQ rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>finance.client-boq.edit-hsn</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Edit client BOQ HSN</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>onboarding.project-setup.edit-scope</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Edit project setup scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Workflow</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>workflow.submittal.review</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Review submittal</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>onboarding.boq.upload</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Upload BOQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>finance.payment.bulk-batch-export</t>
+        </is>
+      </c>
       <c r="D140" t="inlineStr">
         <is>
           <t>Export ICICI bulk-payment batch</t>
@@ -25330,7 +30134,6 @@
           <t>onboarding.boq.upload</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>Upload BOQ</t>
@@ -27846,7 +32649,6 @@
           <t>finance.payment.bulk-batch-export</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>Export ICICI bulk-payment batch</t>
@@ -30340,7 +35142,6 @@
           <t>finance.payment.bulk-batch-export</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>Export ICICI bulk-payment batch</t>
@@ -32650,7 +37451,6 @@
           <t>pmc.measurement.create</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>Create measurement / RA bill</t>
@@ -32668,7 +37468,6 @@
           <t>pmc.measurement.add-items</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>Add measured quantities to RA bill</t>
@@ -32686,7 +37485,6 @@
           <t>finance.client-boq.edit-rate</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>Edit client BOQ rate</t>
@@ -32704,7 +37502,6 @@
           <t>finance.client-boq.edit-hsn</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>Edit client BOQ HSN</t>
@@ -32722,7 +37519,6 @@
           <t>onboarding.project-setup.edit-scope</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>Edit project setup scope</t>
@@ -32740,7 +37536,6 @@
           <t>workflow.submittal.review</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>Review submittal</t>
@@ -32758,7 +37553,6 @@
           <t>onboarding.boq.upload</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>Upload BOQ</t>
@@ -32776,7 +37570,6 @@
           <t>finance.payment.bulk-batch-export</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>Export ICICI bulk-payment batch</t>
@@ -35086,7 +39879,6 @@
           <t>pmc.measurement.create</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>Create measurement / RA bill</t>
@@ -35104,7 +39896,6 @@
           <t>pmc.measurement.add-items</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>Add measured quantities to RA bill</t>
@@ -35122,7 +39913,6 @@
           <t>finance.client-boq.edit-rate</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>Edit client BOQ rate</t>
@@ -35140,7 +39930,6 @@
           <t>finance.client-boq.edit-hsn</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>Edit client BOQ HSN</t>
@@ -35158,7 +39947,6 @@
           <t>onboarding.project-setup.edit-scope</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>Edit project setup scope</t>
@@ -35176,7 +39964,6 @@
           <t>workflow.submittal.review</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>Review submittal</t>
@@ -35194,7 +39981,6 @@
           <t>onboarding.boq.upload</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>Upload BOQ</t>
@@ -35212,7 +39998,6 @@
           <t>finance.payment.bulk-batch-export</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>Export ICICI bulk-payment batch</t>
@@ -37522,7 +42307,6 @@
           <t>pmc.measurement.create</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>Create measurement / RA bill</t>
@@ -37540,7 +42324,6 @@
           <t>pmc.measurement.add-items</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>Add measured quantities to RA bill</t>
@@ -37558,7 +42341,6 @@
           <t>finance.client-boq.edit-rate</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>Edit client BOQ rate</t>
@@ -37576,7 +42358,6 @@
           <t>finance.client-boq.edit-hsn</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>Edit client BOQ HSN</t>
@@ -37594,7 +42375,6 @@
           <t>onboarding.project-setup.edit-scope</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>Edit project setup scope</t>
@@ -37612,7 +42392,6 @@
           <t>workflow.submittal.review</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>Review submittal</t>
@@ -37630,7 +42409,6 @@
           <t>onboarding.boq.upload</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>Upload BOQ</t>
@@ -37648,7 +42426,6 @@
           <t>finance.payment.bulk-batch-export</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>Export ICICI bulk-payment batch</t>
